--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_career.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_career.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="116">
   <si>
     <t>id</t>
   </si>
@@ -92,7 +92,118 @@
     <t>职业的名称</t>
   </si>
   <si>
-    <t>1剑士 2魔法师 3弓箭手 4魔剑士 5圣导师   6召唤师</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>剑士</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>魔法师</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>弓箭手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>魔剑士</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>圣导师</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">   6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>召唤师</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>白法</t>
+    </r>
   </si>
   <si>
     <t>表示在该职业树的第几层</t>
@@ -201,22 +312,148 @@
     <t>转职到本职业的要求等级</t>
   </si>
   <si>
-    <t>人物升到level字段设定等级且未达到当前职业时是否能获得经验（如果level字段数据位空则不受该字段影响）
-0或不填：不可获得经验
-1:未完成转职，可获得经验#经验最多存储到当前升级经验的n% 
-2:未完成转职，可获得经验且正常升级</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人物升到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>level</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>字段设定等级且未达到当前职业时是否能获得经验（如果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>level</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>字段数据位空则不受该字段影响）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>或不填：不可获得经验</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>未完成转职，可获得经验</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>#</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>经验最多存储到当前升级经验的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>n% 
+2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>未完成转职，可获得经验且正常升级</t>
+    </r>
   </si>
   <si>
     <t>格式：属性点数</t>
   </si>
   <si>
-    <t>填写该职业所开放的穿戴栏；填空则不开放穿戴栏（cfg_wearing_bar/id）；</t>
+    <r>
+      <t>填写该职业所开放的穿戴栏；填空则不开放穿戴栏（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>cfg_wearing_bar/id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）；</t>
+    </r>
   </si>
   <si>
     <t>引援cfg_model_default</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>自由分配推荐加点</t>
     </r>
     <r>
@@ -546,9 +783,6 @@
     <t>4#2#0#0#0</t>
   </si>
   <si>
-    <t>可分配的职业点数0点</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -659,24 +893,18 @@
     <t>0#2#0#5#0|5#2#0#0#0</t>
   </si>
   <si>
-    <t>剑魔</t>
-  </si>
-  <si>
     <t>剑圣</t>
   </si>
   <si>
+    <t>可分配的职业点数70点</t>
+  </si>
+  <si>
     <t>圣导师</t>
   </si>
   <si>
-    <t>12#9</t>
-  </si>
-  <si>
     <t>4#1#0#0#0</t>
   </si>
   <si>
-    <t>圣徒</t>
-  </si>
-  <si>
     <t>祭祀</t>
   </si>
   <si>
@@ -692,13 +920,10 @@
     <t>光明法师</t>
   </si>
   <si>
+    <t>圣光法师</t>
+  </si>
+  <si>
     <t>圣光导师</t>
-  </si>
-  <si>
-    <t>神官</t>
-  </si>
-  <si>
-    <t>天国主教</t>
   </si>
 </sst>
 </file>
@@ -711,7 +936,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -739,6 +964,11 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1210,137 +1440,137 @@
     <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1364,6 +1594,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1907,7 +2139,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T29"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="11" width="16.4285714285714" customWidth="1"/>
@@ -2000,13 +2232,13 @@
       <c r="F2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="4" t="s">
         <v>27</v>
       </c>
       <c r="J2" s="1" t="s">
@@ -2282,7 +2514,7 @@
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P7" s="2">
         <v>55</v>
@@ -2290,10 +2522,10 @@
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>62</v>
@@ -2302,7 +2534,7 @@
         <v>67</v>
       </c>
       <c r="E8" s="2">
-        <v>666614</v>
+        <v>666610</v>
       </c>
       <c r="F8" s="7">
         <v>380</v>
@@ -2315,7 +2547,7 @@
         <v>65</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>75</v>
@@ -2324,7 +2556,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P8" s="2">
         <v>55</v>
@@ -2335,7 +2567,7 @@
         <v>69</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>69</v>
@@ -2358,7 +2590,7 @@
         <v>69</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P9" s="2">
         <v>55</v>
@@ -2366,10 +2598,10 @@
     </row>
     <row r="10" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>69</v>
@@ -2394,7 +2626,7 @@
         <v>69</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L10" s="2">
         <v>1</v>
@@ -2410,10 +2642,10 @@
     </row>
     <row r="11" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>69</v>
@@ -2435,10 +2667,10 @@
         <v>65</v>
       </c>
       <c r="J11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="L11" s="2">
         <v>1</v>
@@ -2446,7 +2678,7 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P11" s="2">
         <v>55</v>
@@ -2454,10 +2686,10 @@
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>90</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>69</v>
@@ -2466,7 +2698,7 @@
         <v>67</v>
       </c>
       <c r="E12" s="2">
-        <v>666614</v>
+        <v>666610</v>
       </c>
       <c r="F12" s="7">
         <v>380</v>
@@ -2479,16 +2711,16 @@
         <v>65</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L12" s="2">
         <v>1</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P12" s="2">
         <v>55</v>
@@ -2502,7 +2734,7 @@
         <v>73</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>73</v>
@@ -2524,7 +2756,7 @@
         <v>73</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P13" s="2">
         <v>55</v>
@@ -2533,10 +2765,10 @@
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>73</v>
@@ -2561,7 +2793,7 @@
         <v>73</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L14" s="2">
         <v>1</v>
@@ -2578,10 +2810,10 @@
     </row>
     <row r="15" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A15" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>73</v>
@@ -2603,10 +2835,10 @@
         <v>65</v>
       </c>
       <c r="J15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="K15" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="L15" s="2">
         <v>1</v>
@@ -2614,7 +2846,7 @@
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P15" s="2">
         <v>55</v>
@@ -2623,10 +2855,10 @@
     </row>
     <row r="16" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A16" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>102</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>73</v>
@@ -2635,7 +2867,7 @@
         <v>67</v>
       </c>
       <c r="E16" s="2">
-        <v>666614</v>
+        <v>666610</v>
       </c>
       <c r="F16" s="7">
         <v>380</v>
@@ -2648,16 +2880,16 @@
         <v>65</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L16" s="2">
         <v>1</v>
       </c>
       <c r="O16" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P16" s="2">
         <v>55</v>
@@ -2669,7 +2901,7 @@
         <v>401</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>67</v>
@@ -2691,7 +2923,7 @@
         <v>67</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P17" s="2">
         <v>55</v>
@@ -2703,17 +2935,19 @@
         <v>402</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>67</v>
+        <v>105</v>
+      </c>
+      <c r="C18" s="2">
+        <v>4</v>
       </c>
       <c r="D18" s="2">
         <v>2</v>
       </c>
-      <c r="E18" s="2"/>
+      <c r="E18" s="2">
+        <v>666610</v>
+      </c>
       <c r="F18" s="7">
-        <v>150</v>
+        <v>380</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>69</v>
@@ -2726,15 +2960,15 @@
         <v>67</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L18" s="2">
         <v>1</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
-      <c r="O18" s="2" t="s">
-        <v>70</v>
+      <c r="O18" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="P18" s="2">
         <v>55</v>
@@ -2743,138 +2977,134 @@
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A19" s="2">
-        <v>403</v>
-      </c>
-      <c r="B19" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C19" s="2">
-        <v>4</v>
-      </c>
-      <c r="D19" s="2">
-        <v>3</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="7">
-        <v>220</v>
+      <c r="C19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="2" t="s">
         <v>65</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="L19" s="2">
-        <v>1</v>
-      </c>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="5" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="P19" s="2">
         <v>55</v>
       </c>
-      <c r="T19" s="5"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A20" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>64</v>
+        <v>109</v>
+      </c>
+      <c r="C20" s="2">
+        <v>5</v>
+      </c>
+      <c r="D20" s="2">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2">
+        <v>666610</v>
+      </c>
+      <c r="F20" s="7">
+        <v>380</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="2" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="L20" s="2">
+        <v>1</v>
+      </c>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="P20" s="2">
         <v>55</v>
       </c>
+      <c r="T20" s="5"/>
     </row>
-    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:20">
+    <row r="21" s="2" customFormat="1" spans="1:20">
       <c r="A21" s="2">
-        <v>502</v>
+        <v>601</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21" s="2">
-        <v>2</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="7">
-        <v>150</v>
+        <v>93</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H21" s="7"/>
+        <v>64</v>
+      </c>
+      <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
         <v>65</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="L21" s="2">
-        <v>1</v>
-      </c>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="P21" s="2">
         <v>55</v>
       </c>
+      <c r="T21" s="5"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A22" s="2">
-        <v>503</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22" s="2">
-        <v>5</v>
-      </c>
-      <c r="D22" s="2">
-        <v>3</v>
-      </c>
-      <c r="E22" s="2"/>
+        <v>602</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="2">
+        <v>6666042</v>
+      </c>
       <c r="F22" s="7">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>69</v>
@@ -2884,117 +3114,119 @@
         <v>65</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="L22" s="2">
         <v>1</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
-      <c r="O22" s="5" t="s">
-        <v>76</v>
+      <c r="O22" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="P22" s="2">
         <v>55</v>
       </c>
       <c r="T22" s="5"/>
     </row>
-    <row r="23" s="2" customFormat="1" spans="1:20">
+    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A23" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
+      </c>
+      <c r="E23" s="2">
+        <v>666610</v>
+      </c>
+      <c r="F23" s="7">
+        <v>380</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H23" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="H23" s="7"/>
       <c r="I23" s="2" t="s">
         <v>65</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="L23" s="2">
+        <v>1</v>
+      </c>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="P23" s="2">
         <v>55</v>
       </c>
       <c r="T23" s="5"/>
     </row>
-    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:20">
+    <row r="24" s="2" customFormat="1" spans="1:20">
       <c r="A24" s="2">
-        <v>602</v>
+        <v>701</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>94</v>
+        <v>113</v>
+      </c>
+      <c r="C24" s="2">
+        <v>7</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="7">
-        <v>150</v>
+        <v>62</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H24" s="7"/>
+        <v>64</v>
+      </c>
       <c r="I24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J24" s="2" t="s">
-        <v>94</v>
+      <c r="J24" s="2">
+        <v>7</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L24" s="2">
-        <v>1</v>
-      </c>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="P24" s="2">
         <v>55</v>
       </c>
-      <c r="T24" s="5"/>
     </row>
     <row r="25" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A25" s="2">
-        <v>603</v>
+        <v>702</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>94</v>
+        <v>114</v>
+      </c>
+      <c r="C25" s="2">
+        <v>7</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E25" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="E25" s="2">
+        <v>6666042</v>
+      </c>
       <c r="F25" s="7">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>69</v>
@@ -3003,44 +3235,47 @@
       <c r="I25" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J25" s="2" t="s">
-        <v>94</v>
+      <c r="J25" s="2">
+        <v>7</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="L25" s="2">
         <v>1</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
-      <c r="O25" s="5" t="s">
-        <v>76</v>
+      <c r="O25" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="P25" s="2">
         <v>55</v>
       </c>
-      <c r="T25" s="5"/>
     </row>
-    <row r="26" s="2" customFormat="1" spans="1:20">
+    <row r="26" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A26" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C26" s="2">
         <v>7</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
+      </c>
+      <c r="E26" s="2">
+        <v>666610</v>
+      </c>
+      <c r="F26" s="7">
+        <v>380</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>64</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="H26" s="7"/>
       <c r="I26" s="2" t="s">
         <v>65</v>
       </c>
@@ -3048,139 +3283,65 @@
         <v>7</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
+      </c>
+      <c r="L26" s="2">
+        <v>1</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="P26" s="2">
         <v>55</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A27" s="2">
-        <v>702</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C27" s="2">
-        <v>7</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E27" s="2">
-        <v>6666042</v>
-      </c>
-      <c r="F27" s="7">
-        <v>150</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H27" s="7"/>
-      <c r="I27" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J27" s="2">
-        <v>7</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="L27" s="2">
-        <v>1</v>
-      </c>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P27" s="2">
-        <v>55</v>
-      </c>
+    <row r="30" spans="1:20">
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
     </row>
-    <row r="28" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A28" s="2">
-        <v>703</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C28" s="2">
-        <v>7</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E28" s="8">
-        <v>666606</v>
-      </c>
-      <c r="F28" s="7">
-        <v>220</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H28" s="7"/>
-      <c r="I28" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J28" s="2">
-        <v>7</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="L28" s="2">
-        <v>1</v>
-      </c>
-      <c r="O28" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="P28" s="2">
-        <v>55</v>
-      </c>
+    <row r="31" spans="1:20">
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
     </row>
-    <row r="29" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A29" s="2">
-        <v>704</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C29" s="2">
-        <v>7</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E29" s="2">
-        <v>666614</v>
-      </c>
-      <c r="F29" s="7">
-        <v>380</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H29" s="7"/>
-      <c r="I29" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J29" s="2">
-        <v>7</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="L29" s="2">
-        <v>1</v>
-      </c>
-      <c r="O29" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="P29" s="2">
-        <v>55</v>
-      </c>
+    <row r="32" spans="1:20">
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+    </row>
+    <row r="33" spans="3:6">
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+    </row>
+    <row r="34" spans="3:6">
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+    </row>
+    <row r="35" spans="3:6">
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="10"/>
+    </row>
+    <row r="36" spans="3:6">
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+    </row>
+    <row r="37" spans="3:6">
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E6">
@@ -3195,13 +3356,10 @@
   <conditionalFormatting sqref="E15">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E28">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26:A29">
+  <conditionalFormatting sqref="A24:A26">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A25 A30:A1048576">
+  <conditionalFormatting sqref="A1:A23 A27:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_career.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_career.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="14970" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_career" sheetId="1" r:id="rId1"/>
@@ -425,6 +425,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>填写该职业所开放的穿戴栏；填空则不开放穿戴栏（</t>
     </r>
     <r>
@@ -744,7 +749,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>剑士</t>
+    <t>Swordsman</t>
   </si>
   <si>
     <t/>
@@ -759,7 +764,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>骑士</t>
+    <t>Knight</t>
   </si>
   <si>
     <t>2</t>
@@ -771,7 +776,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>神骑士</t>
+    <t>Blade Knight</t>
   </si>
   <si>
     <t>3</t>
@@ -786,7 +791,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>圣殿武士</t>
+    <t>Temple Knight</t>
   </si>
   <si>
     <t>301</t>
@@ -818,7 +823,7 @@
     </r>
   </si>
   <si>
-    <t>魔法师</t>
+    <t>Magician</t>
   </si>
   <si>
     <t>0#2#0#3#0</t>
@@ -827,13 +832,13 @@
     <t>5</t>
   </si>
   <si>
-    <t>魔导师</t>
+    <t>Wizard</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>神导士</t>
+    <t>Soul Master</t>
   </si>
   <si>
     <t>202</t>
@@ -845,13 +850,13 @@
     <t>8</t>
   </si>
   <si>
-    <t>大法师</t>
+    <t>Archmage</t>
   </si>
   <si>
     <t>302</t>
   </si>
   <si>
-    <t>弓箭手</t>
+    <t>Elf</t>
   </si>
   <si>
     <t>1#4#0#0#0</t>
@@ -860,7 +865,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>圣射手</t>
+    <t>Muse Elf</t>
   </si>
   <si>
     <t>1#4#0#0#0|0#1#0#4#0</t>
@@ -869,7 +874,7 @@
     <t>12</t>
   </si>
   <si>
-    <t>神射手</t>
+    <t>High Elf</t>
   </si>
   <si>
     <t>203</t>
@@ -881,49 +886,49 @@
     <t>9</t>
   </si>
   <si>
-    <t>精灵游侠</t>
+    <t>Elf Ranger</t>
   </si>
   <si>
     <t>303</t>
   </si>
   <si>
-    <t>魔剑士</t>
+    <t>Magic Gladiator</t>
   </si>
   <si>
     <t>0#2#0#5#0|5#2#0#0#0</t>
   </si>
   <si>
-    <t>剑圣</t>
+    <t>Blade Master</t>
   </si>
   <si>
     <t>可分配的职业点数70点</t>
   </si>
   <si>
-    <t>圣导师</t>
+    <t>Lord Emperor</t>
   </si>
   <si>
     <t>4#1#0#0#0</t>
   </si>
   <si>
-    <t>祭祀</t>
-  </si>
-  <si>
-    <t>召唤术师</t>
-  </si>
-  <si>
-    <t>召唤导师</t>
-  </si>
-  <si>
-    <t>召唤巫师</t>
-  </si>
-  <si>
-    <t>光明法师</t>
-  </si>
-  <si>
-    <t>圣光法师</t>
-  </si>
-  <si>
-    <t>圣光导师</t>
+    <t>Priest</t>
+  </si>
+  <si>
+    <t>Summoner</t>
+  </si>
+  <si>
+    <t>Summon Master</t>
+  </si>
+  <si>
+    <t>Summon Wizard</t>
+  </si>
+  <si>
+    <t>Light Mage</t>
+  </si>
+  <si>
+    <t>Holy Mage</t>
+  </si>
+  <si>
+    <t>Holy Master</t>
   </si>
 </sst>
 </file>
@@ -1570,7 +1575,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1582,14 +1587,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2403,7 +2409,7 @@
       <c r="A5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -2480,7 +2486,7 @@
       <c r="A7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>72</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -2513,7 +2519,7 @@
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="8" t="s">
         <v>70</v>
       </c>
       <c r="P7" s="2">
@@ -2555,7 +2561,7 @@
       <c r="L8" s="2">
         <v>1</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="O8" s="8" t="s">
         <v>79</v>
       </c>
       <c r="P8" s="2">
@@ -2566,7 +2572,7 @@
       <c r="A9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="5" t="s">
         <v>80</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -2644,7 +2650,7 @@
       <c r="A11" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="5" t="s">
         <v>85</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -2653,7 +2659,7 @@
       <c r="D11" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="9">
         <v>666606</v>
       </c>
       <c r="F11" s="7">
@@ -2677,7 +2683,7 @@
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
-      <c r="O11" s="5" t="s">
+      <c r="O11" s="8" t="s">
         <v>70</v>
       </c>
       <c r="P11" s="2">
@@ -2719,7 +2725,7 @@
       <c r="L12" s="2">
         <v>1</v>
       </c>
-      <c r="O12" s="5" t="s">
+      <c r="O12" s="8" t="s">
         <v>79</v>
       </c>
       <c r="P12" s="2">
@@ -2733,7 +2739,7 @@
       <c r="A13" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -2761,7 +2767,7 @@
       <c r="P13" s="2">
         <v>55</v>
       </c>
-      <c r="T13" s="5"/>
+      <c r="T13" s="8"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A14" s="2" t="s">
@@ -2806,13 +2812,13 @@
       <c r="P14" s="2">
         <v>55</v>
       </c>
-      <c r="T14" s="5"/>
+      <c r="T14" s="8"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A15" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="5" t="s">
         <v>97</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -2821,7 +2827,7 @@
       <c r="D15" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="9">
         <v>666606</v>
       </c>
       <c r="F15" s="7">
@@ -2845,13 +2851,13 @@
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
-      <c r="O15" s="5" t="s">
+      <c r="O15" s="8" t="s">
         <v>70</v>
       </c>
       <c r="P15" s="2">
         <v>55</v>
       </c>
-      <c r="T15" s="5"/>
+      <c r="T15" s="8"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A16" s="2" t="s">
@@ -2888,19 +2894,19 @@
       <c r="L16" s="2">
         <v>1</v>
       </c>
-      <c r="O16" s="5" t="s">
+      <c r="O16" s="8" t="s">
         <v>79</v>
       </c>
       <c r="P16" s="2">
         <v>55</v>
       </c>
-      <c r="T16" s="5"/>
+      <c r="T16" s="8"/>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:20">
       <c r="A17" s="2">
         <v>401</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="5" t="s">
         <v>103</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -2928,7 +2934,7 @@
       <c r="P17" s="2">
         <v>55</v>
       </c>
-      <c r="T17" s="5"/>
+      <c r="T17" s="8"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A18" s="2">
@@ -2967,19 +2973,19 @@
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
-      <c r="O18" s="5" t="s">
+      <c r="O18" s="8" t="s">
         <v>106</v>
       </c>
       <c r="P18" s="2">
         <v>55</v>
       </c>
-      <c r="T18" s="5"/>
+      <c r="T18" s="8"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A19" s="2">
         <v>501</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="5" t="s">
         <v>107</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3012,7 +3018,7 @@
       <c r="A20" s="2">
         <v>502</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="5" t="s">
         <v>109</v>
       </c>
       <c r="C20" s="2">
@@ -3045,13 +3051,13 @@
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
-      <c r="O20" s="5" t="s">
+      <c r="O20" s="8" t="s">
         <v>106</v>
       </c>
       <c r="P20" s="2">
         <v>55</v>
       </c>
-      <c r="T20" s="5"/>
+      <c r="T20" s="8"/>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:20">
       <c r="A21" s="2">
@@ -3085,7 +3091,7 @@
       <c r="P21" s="2">
         <v>55</v>
       </c>
-      <c r="T21" s="5"/>
+      <c r="T21" s="8"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A22" s="2">
@@ -3130,7 +3136,7 @@
       <c r="P22" s="2">
         <v>55</v>
       </c>
-      <c r="T22" s="5"/>
+      <c r="T22" s="8"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A23" s="2">
@@ -3169,13 +3175,13 @@
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
-      <c r="O23" s="5" t="s">
+      <c r="O23" s="8" t="s">
         <v>106</v>
       </c>
       <c r="P23" s="2">
         <v>55</v>
       </c>
-      <c r="T23" s="5"/>
+      <c r="T23" s="8"/>
     </row>
     <row r="24" s="2" customFormat="1" spans="1:20">
       <c r="A24" s="2">
@@ -3288,7 +3294,7 @@
       <c r="L26" s="2">
         <v>1</v>
       </c>
-      <c r="O26" s="5" t="s">
+      <c r="O26" s="8" t="s">
         <v>106</v>
       </c>
       <c r="P26" s="2">
@@ -3296,52 +3302,52 @@
       </c>
     </row>
     <row r="30" spans="1:20">
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
     </row>
     <row r="31" spans="1:20">
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
     </row>
     <row r="32" spans="1:20">
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
     </row>
     <row r="33" spans="3:6">
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
     </row>
     <row r="34" spans="3:6">
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
     </row>
     <row r="35" spans="3:6">
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="11"/>
     </row>
     <row r="36" spans="3:6">
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
     </row>
     <row r="37" spans="3:6">
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E6">
